--- a/static/bw_amr_ig/StructureDefinition-botswana-amr-diagnostic-report.xlsx
+++ b/static/bw_amr_ig/StructureDefinition-botswana-amr-diagnostic-report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="394">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-09T10:14:37-04:00</t>
+    <t>2026-03-13T15:05:11-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Bundles AMR susceptibility observations into one comprehensive report</t>
+    <t>Bundles AMR culture results into one comprehensive report. References top-level observations (gram stain and organism identifications). Susceptibility and special test results are accessed via OrganismObservation.hasMember.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -439,7 +439,7 @@
     <t>DiagnosticReport.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.3.0)
 </t>
   </si>
   <si>
@@ -477,7 +477,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.3.0</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -498,7 +498,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.3.0</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -541,7 +541,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -670,7 +670,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.3.0|ImmunizationRecommendation|4.3.0|MedicationRequest|4.3.0|NutritionOrder|4.3.0|ServiceRequest|4.3.0)
 </t>
   </si>
   <si>
@@ -751,7 +751,11 @@
     <t>HL7 V2 table 0074</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.3.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -761,6 +765,21 @@
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:microbiologyStudies</t>
+  </si>
+  <si>
+    <t>microbiologyStudies</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="18725-2"/&gt;
+    &lt;display value="Microbiology studies (set)"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -788,7 +807,7 @@
     <t>LOINC Codes for Diagnostic Reports</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/report-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/report-codes|4.3.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -842,7 +861,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-encounter)
 </t>
   </si>
   <si>
@@ -953,7 +972,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam)
+    <t xml:space="preserve">Reference(Organization|Practitioner)
 </t>
   </si>
   <si>
@@ -988,6 +1007,10 @@
 Reported by</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(Practitioner|4.3.0|PractitionerRole|4.3.0|Organization|4.3.0|CareTeam|4.3.0)
+</t>
+  </si>
+  <si>
     <t>Primary result interpreter</t>
   </si>
   <si>
@@ -1029,7 +1052,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation)
+    <t xml:space="preserve">Reference(Observation|4.3.0)
 </t>
   </si>
   <si>
@@ -1075,30 +1098,10 @@
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.result:susceptibility</t>
-  </si>
-  <si>
-    <t>susceptibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-susceptibility-observation)
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.result:specialTests</t>
-  </si>
-  <si>
-    <t>specialTests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-special-test-observation)
-</t>
-  </si>
-  <si>
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ImagingStudy)
+    <t xml:space="preserve">Reference(ImagingStudy|4.3.0)
 </t>
   </si>
   <si>
@@ -1189,7 +1192,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media)
+    <t xml:space="preserve">Reference(Media|4.3.0)
 </t>
   </si>
   <si>
@@ -1236,7 +1239,7 @@
     <t>SNOMED CT Clinical Findings</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.3.0</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>
@@ -1563,12 +1566,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN46"/>
+  <dimension ref="A1:AN45"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.0234375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.05859375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="36.21875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.80078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.69921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="55.23046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.65234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.265625" customWidth="true" bestFit="true"/>
@@ -1576,7 +1579,7 @@
     <col min="8" max="8" width="13.609375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.1796875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="108.9453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="112.67578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1591,7 +1594,7 @@
     <col min="23" max="23" width="16.40625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="15.85546875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="30.55859375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.58203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.8203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.2734375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.55859375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.56640625" customWidth="true" bestFit="true"/>
@@ -4020,7 +4023,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>79</v>
@@ -4082,16 +4085,14 @@
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>229</v>
@@ -4112,25 +4113,27 @@
         <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4152,12 +4155,14 @@
         <v>231</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4167,7 +4172,7 @@
         <v>20</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>20</v>
@@ -4182,13 +4187,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4206,13 +4211,13 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
@@ -4221,28 +4226,28 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>247</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4261,18 +4266,16 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>256</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4281,7 +4284,7 @@
         <v>20</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>20</v>
+        <v>248</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>20</v>
@@ -4296,13 +4299,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>20</v>
+        <v>249</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4320,10 +4323,10 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>90</v>
@@ -4335,32 +4338,32 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>90</v>
@@ -4375,19 +4378,17 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4436,7 +4437,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4451,32 +4452,32 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>90</v>
@@ -4491,19 +4492,19 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4540,17 +4541,19 @@
         <v>20</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>280</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4565,30 +4568,28 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4607,19 +4608,19 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4656,19 +4657,17 @@
         <v>20</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>20</v>
+        <v>284</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4683,32 +4682,34 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="D28" t="s" s="2">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>90</v>
@@ -4723,19 +4724,19 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4784,7 +4785,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4799,35 +4800,35 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4839,19 +4840,19 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>298</v>
+        <v>125</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -4900,13 +4901,13 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
@@ -4915,28 +4916,28 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4955,19 +4956,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5016,7 +5017,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5031,32 +5032,32 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>20</v>
+        <v>312</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>79</v>
@@ -5068,22 +5069,22 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="N31" t="s" s="2">
-        <v>317</v>
-      </c>
       <c r="O31" t="s" s="2">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5132,7 +5133,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5147,28 +5148,28 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>20</v>
+        <v>307</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>259</v>
+        <v>309</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>20</v>
+        <v>310</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>321</v>
+        <v>20</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5187,19 +5188,19 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5236,17 +5237,19 @@
         <v>20</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5264,10 +5267,10 @@
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>329</v>
+        <v>263</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>20</v>
@@ -5275,23 +5278,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5303,19 +5304,19 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5352,19 +5353,17 @@
         <v>20</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5382,10 +5381,10 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -5393,23 +5392,23 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5421,19 +5420,19 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5482,7 +5481,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5500,10 +5499,10 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -5511,20 +5510,20 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>79</v>
@@ -5539,19 +5538,19 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5600,7 +5599,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5618,10 +5617,10 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -5629,16 +5628,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>321</v>
+        <v>20</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5657,20 +5654,18 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -5718,7 +5713,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5736,10 +5731,10 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>328</v>
+        <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
@@ -5747,14 +5742,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>20</v>
+        <v>348</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5770,21 +5765,21 @@
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
@@ -5832,7 +5827,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5844,16 +5839,16 @@
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>353</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>20</v>
+        <v>354</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
@@ -5861,21 +5856,21 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>349</v>
+        <v>20</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -5884,21 +5879,19 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>351</v>
+        <v>104</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>352</v>
+        <v>105</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>353</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
@@ -5946,28 +5939,28 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>348</v>
+        <v>106</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>354</v>
+        <v>20</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>355</v>
+        <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>329</v>
+        <v>107</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -5975,21 +5968,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6001,15 +5994,17 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>357</v>
+        <v>110</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6058,19 +6053,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6094,7 +6089,7 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>109</v>
+        <v>359</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6107,24 +6102,26 @@
         <v>20</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>111</v>
+        <v>360</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>112</v>
+        <v>361</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6172,7 +6169,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>117</v>
+        <v>362</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6193,7 +6190,7 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>107</v>
+        <v>188</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
@@ -6201,45 +6198,45 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>360</v>
+        <v>20</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>110</v>
+        <v>356</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>113</v>
+        <v>366</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>195</v>
+        <v>367</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6294,13 +6291,13 @@
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -6309,7 +6306,7 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>188</v>
+        <v>368</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -6317,10 +6314,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6328,7 +6325,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>90</v>
@@ -6340,23 +6337,19 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6404,10 +6397,10 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>90</v>
@@ -6425,7 +6418,7 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -6433,18 +6426,18 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>20</v>
+        <v>375</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>90</v>
@@ -6456,19 +6449,21 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
       </c>
@@ -6516,10 +6511,10 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>90</v>
@@ -6534,10 +6529,10 @@
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>20</v>
+        <v>379</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -6545,21 +6540,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>376</v>
+        <v>20</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -6571,18 +6566,16 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>357</v>
+        <v>231</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>379</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>20</v>
       </c>
@@ -6606,13 +6599,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>20</v>
+        <v>384</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>20</v>
+        <v>385</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6630,13 +6623,13 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
@@ -6648,10 +6641,10 @@
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -6659,10 +6652,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6685,16 +6678,20 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>231</v>
+        <v>388</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -6718,13 +6715,13 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>385</v>
+        <v>20</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>386</v>
+        <v>20</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -6742,7 +6739,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6760,128 +6757,12 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="P46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AN46" t="s" s="2">
         <v>20</v>
       </c>
     </row>

--- a/static/bw_amr_ig/StructureDefinition-botswana-amr-diagnostic-report.xlsx
+++ b/static/bw_amr_ig/StructureDefinition-botswana-amr-diagnostic-report.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:05:11-04:00</t>
+    <t>2026-03-13T15:54:56-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/static/bw_amr_ig/StructureDefinition-botswana-amr-diagnostic-report.xlsx
+++ b/static/bw_amr_ig/StructureDefinition-botswana-amr-diagnostic-report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="354">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-diagnostic-report</t>
+    <t>http://bw.health.gov/fhir/amr/StructureDefinition/botswana-amr-diagnostic-report</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:54:56-04:00</t>
+    <t>2026-03-13T21:27:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -330,22 +330,110 @@
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.meta.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.meta.extension</t>
+    <t>DiagnosticReport.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>IETF language tag</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension</t>
   </si>
   <si>
     <t>extensions
@@ -359,259 +447,19 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
+    <t>DomainResource.extension</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>DiagnosticReport.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.3.0)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>http://bw.health.gov/fhir/StructureDefinition/BotswanaAMR-DiagnosticReport</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.3.0</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.3.0</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>IETF language tag</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
     <t>DiagnosticReport.modifierExtension</t>
   </si>
   <si>
@@ -748,6 +596,9 @@
     <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
   </si>
   <si>
+    <t>example</t>
+  </si>
+  <si>
     <t>HL7 V2 table 0074</t>
   </si>
   <si>
@@ -756,6 +607,9 @@
   <si>
     <t xml:space="preserve">pattern:$this}
 </t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -798,8 +652,8 @@
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="58321-0"/&gt;
-    &lt;display value="Bacteria identified and antimicrobial susceptibility panel"/&gt;
+    &lt;code value="85421-6"/&gt;
+    &lt;display value="Bacterial identification and susceptibility panel - Isolate"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -829,7 +683,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-patient)
+    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/amr/StructureDefinition/botswana-amr-patient)
 </t>
   </si>
   <si>
@@ -861,7 +715,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-encounter)
+    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/amr/StructureDefinition/botswana-amr-encounter)
 </t>
   </si>
   <si>
@@ -944,6 +798,10 @@
 Date IssuedDate Verified</t>
   </si>
   <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
     <t>DateTime this version was made</t>
   </si>
   <si>
@@ -1026,7 +884,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-specimen)
+    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/amr/StructureDefinition/botswana-amr-specimen)
 </t>
   </si>
   <si>
@@ -1084,7 +942,7 @@
     <t>gramStain</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-gram-stain-observation)
+    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/amr/StructureDefinition/botswana-amr-gram-stain-observation)
 </t>
   </si>
   <si>
@@ -1094,7 +952,7 @@
     <t>organism</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-organism-observation)
+    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/amr/StructureDefinition/botswana-amr-organism-observation)
 </t>
   </si>
   <si>
@@ -1151,7 +1009,25 @@
 </t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>DiagnosticReport.media.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
   </si>
   <si>
     <t>DiagnosticReport.media.modifierExtension</t>
@@ -1566,7 +1442,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN45"/>
+  <dimension ref="A1:AN37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.05859375" customWidth="true" bestFit="true"/>
@@ -1597,7 +1473,7 @@
     <col min="26" max="26" width="50.8203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.2734375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.55859375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.56640625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.16015625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.3671875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="11.84375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="31.2109375" customWidth="true" bestFit="true" hidden="true"/>
@@ -2094,21 +1970,23 @@
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N5" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N5" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>20</v>
@@ -2157,7 +2035,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2169,7 +2047,7 @@
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2178,7 +2056,7 @@
         <v>20</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>20</v>
@@ -2186,21 +2064,21 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2247,28 +2125,28 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>117</v>
@@ -2277,13 +2155,13 @@
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2292,7 +2170,7 @@
         <v>20</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>20</v>
@@ -2300,14 +2178,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2323,19 +2201,19 @@
         <v>20</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2385,7 +2263,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2406,7 +2284,7 @@
         <v>20</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>20</v>
@@ -2414,21 +2292,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2437,19 +2315,19 @@
         <v>20</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2499,19 +2377,19 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>20</v>
@@ -2520,7 +2398,7 @@
         <v>20</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>20</v>
@@ -2528,21 +2406,21 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2551,19 +2429,19 @@
         <v>20</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2613,19 +2491,19 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2634,7 +2512,7 @@
         <v>20</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>20</v>
@@ -2642,14 +2520,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2662,24 +2540,26 @@
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O10" s="2"/>
+      <c r="O10" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
       </c>
@@ -2688,7 +2568,7 @@
         <v>20</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="T10" t="s" s="2">
         <v>20</v>
@@ -2727,7 +2607,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2739,7 +2619,7 @@
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2748,7 +2628,7 @@
         <v>20</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>20</v>
@@ -2756,14 +2636,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2782,18 +2662,20 @@
         <v>91</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="O11" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
       </c>
@@ -2817,29 +2699,31 @@
         <v>20</v>
       </c>
       <c r="X11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="Y11" s="2"/>
-      <c r="Z11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2854,28 +2738,28 @@
         <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2891,21 +2775,23 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O12" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
       </c>
@@ -2929,11 +2815,13 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y12" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z12" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>20</v>
@@ -2951,7 +2839,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2966,13 +2854,13 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>20</v>
@@ -2980,10 +2868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2991,7 +2879,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>90</v>
@@ -3006,18 +2894,18 @@
         <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O13" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
       </c>
@@ -3026,7 +2914,7 @@
         <v>20</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>20</v>
@@ -3041,13 +2929,13 @@
         <v>20</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>20</v>
@@ -3065,10 +2953,10 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>90</v>
@@ -3080,35 +2968,35 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>20</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3117,19 +3005,19 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3155,37 +3043,35 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
@@ -3197,29 +3083,31 @@
         <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>20</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="D15" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>90</v>
@@ -3231,19 +3119,19 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3254,7 +3142,7 @@
         <v>20</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>20</v>
@@ -3269,13 +3157,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3293,13 +3181,13 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
@@ -3311,32 +3199,32 @@
         <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>20</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3345,20 +3233,18 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>182</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3368,7 +3254,7 @@
         <v>20</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>20</v>
+        <v>201</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>20</v>
@@ -3383,13 +3269,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>20</v>
+        <v>203</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3407,50 +3293,50 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>187</v>
+        <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3459,21 +3345,21 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>111</v>
+        <v>211</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3521,74 +3407,74 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>20</v>
+        <v>214</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>20</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>109</v>
+        <v>219</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J18" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="J18" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K18" t="s" s="2">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>113</v>
+        <v>223</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3637,50 +3523,50 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3692,19 +3578,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3741,25 +3627,23 @@
         <v>20</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -3768,35 +3652,37 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>205</v>
+        <v>239</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>207</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -3805,22 +3691,22 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3869,13 +3755,13 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
@@ -3884,32 +3770,32 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>20</v>
+        <v>245</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>90</v>
@@ -3918,23 +3804,25 @@
         <v>20</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>164</v>
+        <v>246</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O21" t="s" s="2">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -3944,7 +3832,7 @@
         <v>20</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>20</v>
@@ -3959,13 +3847,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>223</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>224</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -3983,10 +3871,10 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>90</v>
@@ -3998,32 +3886,32 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>228</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>79</v>
@@ -4038,18 +3926,20 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
       </c>
@@ -4073,29 +3963,31 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AC22" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4110,37 +4002,35 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>240</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>230</v>
+        <v>266</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4152,18 +4042,20 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
@@ -4172,7 +4064,7 @@
         <v>20</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>20</v>
@@ -4187,13 +4079,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4211,7 +4103,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4226,35 +4118,35 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>240</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>245</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>90</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4263,19 +4155,23 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4284,7 +4180,7 @@
         <v>20</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>248</v>
+        <v>20</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>20</v>
@@ -4299,13 +4195,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4323,13 +4219,13 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
@@ -4338,35 +4234,35 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>251</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>253</v>
+        <v>216</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>254</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>90</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4375,20 +4271,22 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O25" t="s" s="2">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4425,25 +4323,23 @@
         <v>20</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -4452,28 +4348,30 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="D26" t="s" s="2">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4489,22 +4387,22 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4553,13 +4451,13 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
@@ -4568,35 +4466,37 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>272</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>275</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="D27" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>90</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4605,22 +4505,22 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4657,23 +4557,25 @@
         <v>20</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AC27" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>284</v>
+        <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
@@ -4682,37 +4584,35 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>288</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4721,23 +4621,21 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -4785,13 +4683,13 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
@@ -4800,35 +4698,35 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>288</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4840,19 +4738,17 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>125</v>
+        <v>303</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -4901,50 +4797,50 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>102</v>
+        <v>307</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>299</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>301</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -4953,23 +4849,19 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5017,43 +4909,43 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>308</v>
+        <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>310</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>312</v>
+        <v>136</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5069,23 +4961,21 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>313</v>
+        <v>137</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>314</v>
+        <v>138</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5133,7 +5023,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5145,19 +5035,19 @@
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>317</v>
+        <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>310</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -5169,11 +5059,11 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>20</v>
+        <v>319</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>79</v>
@@ -5182,13 +5072,13 @@
         <v>20</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>319</v>
+        <v>137</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>320</v>
@@ -5197,10 +5087,10 @@
         <v>321</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>322</v>
+        <v>140</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>323</v>
+        <v>146</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5249,7 +5139,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5261,16 +5151,16 @@
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>324</v>
+        <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>20</v>
@@ -5278,22 +5168,22 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>326</v>
+        <v>20</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G33" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G33" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5304,19 +5194,19 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O33" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5353,23 +5243,25 @@
         <v>20</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -5381,10 +5273,10 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -5392,20 +5284,18 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>326</v>
+        <v>20</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>90</v>
@@ -5417,23 +5307,19 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5481,13 +5367,13 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -5499,10 +5385,10 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -5510,24 +5396,22 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G35" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G35" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5538,19 +5422,17 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5599,13 +5481,13 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
@@ -5617,10 +5499,10 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -5654,17 +5536,15 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M36" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>345</v>
-      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5689,13 +5569,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>20</v>
+        <v>344</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>20</v>
+        <v>345</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -5731,7 +5611,7 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>20</v>
+        <v>339</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>346</v>
@@ -5749,7 +5629,7 @@
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>348</v>
+        <v>20</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5765,18 +5645,20 @@
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
         <v>352</v>
       </c>
@@ -5839,930 +5721,18 @@
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AK37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="AN37" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q38" s="2"/>
-      <c r="R38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O39" s="2"/>
-      <c r="P39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q39" s="2"/>
-      <c r="R39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="P40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="P41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q41" s="2"/>
-      <c r="R41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
-      <c r="P42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q42" s="2"/>
-      <c r="R42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="P43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="P45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AN45" t="s" s="2">
         <v>20</v>
       </c>
     </row>
